--- a/ruci_europe.xlsx
+++ b/ruci_europe.xlsx
@@ -1,25 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vince\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{70E51F71-74E8-448F-8226-24FDB3D11A37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{0E263AB2-3332-487F-9091-D2B7C1BF69AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8865" yWindow="2760" windowWidth="23010" windowHeight="17280" xr2:uid="{00110A5E-AFDB-4011-9ECE-C80D70C73172}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="European_RUCI" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
-      <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
         <xcalcf:feature name="microsoft.com:RD"/>
@@ -31,15 +28,12 @@
         <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="2"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t>month</t>
   </si>
@@ -474,17 +468,20 @@
   </si>
   <si>
     <t>2025-12</t>
+  </si>
+  <si>
+    <t>2015-07</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -492,6 +489,12 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
@@ -539,7 +542,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -562,44 +565,44 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
@@ -626,32 +629,14 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
@@ -678,24 +663,6 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
-        <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -707,168 +674,172 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:satMod val="105000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="103000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:satMod val="109000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
         </a:gradFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:satMod val="103000"/>
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:satMod val="110000"/>
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:satMod val="120000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
-            <a:schemeClr val="phClr"/>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
-        </a:effectStyle>
-        <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
               <a:srgbClr val="000000">
-                <a:alpha val="63000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-            <a:satMod val="170000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:satMod val="150000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:satMod val="130000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
-                <a:satMod val="120000"/>
+                <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+                <a:satMod val="300000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+                <a:satMod val="200000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
-  <a:extLst>
-    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
-    </a:ext>
-  </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BFBEFB8E-0714-4410-B5D2-F08749FB402C}">
-  <dimension ref="A1:B144"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:B145"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -1025,1005 +996,1015 @@
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>20</v>
+        <v>145</v>
       </c>
       <c r="B20">
-        <v>15.148298866030331</v>
+        <f t="shared" ref="B20" si="0">AVERAGE(B19,B21)</f>
+        <v>26.619396865278219</v>
       </c>
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B21">
-        <v>34.504386618695463</v>
+        <v>15.148298866030331</v>
       </c>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B22">
-        <v>30.455368602691092</v>
+        <v>34.504386618695463</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B23">
-        <v>20.514231835512909</v>
+        <v>30.455368602691092</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24">
-        <v>21.858099462665571</v>
+        <v>20.514231835512909</v>
       </c>
     </row>
     <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25">
-        <v>16.339391195938919</v>
+        <v>21.858099462665571</v>
       </c>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B26">
-        <v>18.771266191858579</v>
+        <v>16.339391195938919</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27">
-        <v>14.094150903444371</v>
+        <v>18.771266191858579</v>
       </c>
     </row>
     <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="B28">
-        <v>19.367784623813669</v>
+        <v>14.094150903444371</v>
       </c>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="B29">
-        <v>10.08234649442241</v>
+        <v>19.367784623813669</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B30">
-        <v>17.401509313813339</v>
+        <v>10.08234649442241</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="B31">
-        <v>17.548235250929061</v>
+        <v>17.401509313813339</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="B32">
-        <v>23.21627256098461</v>
+        <v>17.548235250929061</v>
       </c>
     </row>
     <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="B33">
-        <v>17.624275201863021</v>
+        <v>23.21627256098461</v>
       </c>
     </row>
     <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="B34">
-        <v>28.895644352769281</v>
+        <v>17.624275201863021</v>
       </c>
     </row>
     <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="B35">
-        <v>21.67342698321352</v>
+        <v>28.895644352769281</v>
       </c>
     </row>
     <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="B36">
-        <v>29.399918230461029</v>
+        <v>21.67342698321352</v>
       </c>
     </row>
     <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="B37">
-        <v>18.761463602823429</v>
+        <v>29.399918230461029</v>
       </c>
     </row>
     <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38">
-        <v>24.16714916258568</v>
+        <v>18.761463602823429</v>
       </c>
     </row>
     <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39">
-        <v>17.737415854372891</v>
+        <v>24.16714916258568</v>
       </c>
     </row>
     <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40">
-        <v>12.30980546718429</v>
+        <v>17.737415854372891</v>
       </c>
     </row>
     <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41">
-        <v>17.831179320957439</v>
+        <v>12.30980546718429</v>
       </c>
     </row>
     <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B42">
-        <v>14.41773307017051</v>
+        <v>17.831179320957439</v>
       </c>
     </row>
     <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="B43">
-        <v>21.543934748744061</v>
+        <v>14.41773307017051</v>
       </c>
     </row>
     <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="B44">
-        <v>25.95144386216479</v>
+        <v>21.543934748744061</v>
       </c>
     </row>
     <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="B45">
-        <v>16.577908068537681</v>
+        <v>25.95144386216479</v>
       </c>
     </row>
     <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="B46">
-        <v>11.84585443372497</v>
+        <v>16.577908068537681</v>
       </c>
     </row>
     <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B47">
-        <v>13.00529713292827</v>
+        <v>11.84585443372497</v>
       </c>
     </row>
     <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B48">
-        <v>10.765471716555091</v>
+        <v>13.00529713292827</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B49">
-        <v>11.41746299181133</v>
+        <v>10.765471716555091</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B50">
-        <v>14.24400838706951</v>
+        <v>11.41746299181133</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="B51">
-        <v>38.522935955928858</v>
+        <v>14.24400838706951</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="B52">
-        <v>17.784032645411909</v>
+        <v>38.522935955928858</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B53">
-        <v>24.70365065785218</v>
+        <v>17.784032645411909</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B54">
-        <v>18.596770631413349</v>
+        <v>24.70365065785218</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B55">
-        <v>22.44131385812322</v>
+        <v>18.596770631413349</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B56">
-        <v>21.681785626080359</v>
+        <v>22.44131385812322</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B57">
-        <v>5.0497035083663553</v>
+        <v>21.681785626080359</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B58">
-        <v>18.47762157417624</v>
+        <v>5.0497035083663553</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="B59">
-        <v>36.895782093929398</v>
+        <v>18.47762157417624</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="B60">
-        <v>7.8994200136642574</v>
+        <v>36.895782093929398</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B61">
-        <v>8.7914309289186434</v>
+        <v>7.8994200136642574</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B62">
-        <v>8.0205307294427168</v>
+        <v>8.7914309289186434</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B63">
-        <v>10.11475113902647</v>
+        <v>8.0205307294427168</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B64">
-        <v>13.88638589779405</v>
+        <v>10.11475113902647</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="B65">
-        <v>7.4327054265632233</v>
+        <v>13.88638589779405</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="B66">
-        <v>27.216857321407179</v>
+        <v>7.4327054265632233</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="B67">
-        <v>6.9393919267650697</v>
+        <v>27.216857321407179</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="B68">
-        <v>15.465950806559389</v>
+        <v>6.9393919267650697</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B69">
-        <v>19.37229572210806</v>
+        <v>15.465950806559389</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B70">
-        <v>18.36368436789186</v>
+        <v>19.37229572210806</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B71">
-        <v>9.3703321432469622</v>
+        <v>18.36368436789186</v>
       </c>
     </row>
     <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="B72">
-        <v>23.983774551423028</v>
+        <v>9.3703321432469622</v>
       </c>
     </row>
     <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B73">
-        <v>17.27429388236903</v>
+        <v>23.983774551423028</v>
       </c>
     </row>
     <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B74">
-        <v>13.05060469827233</v>
+        <v>17.27429388236903</v>
       </c>
     </row>
     <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="B75">
-        <v>2.205763358058888</v>
+        <v>13.05060469827233</v>
       </c>
     </row>
     <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B76">
-        <v>14.461360029932431</v>
+        <v>2.205763358058888</v>
       </c>
     </row>
     <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B77">
-        <v>5.1141357984223852</v>
+        <v>14.461360029932431</v>
       </c>
     </row>
     <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B78">
-        <v>9.5081219736406855</v>
+        <v>5.1141357984223852</v>
       </c>
     </row>
     <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B79">
-        <v>3.9234420110432349</v>
+        <v>9.5081219736406855</v>
       </c>
     </row>
     <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B80">
-        <v>12.15249495419487</v>
+        <v>3.9234420110432349</v>
       </c>
     </row>
     <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B81">
-        <v>15.60889818841282</v>
+        <v>12.15249495419487</v>
       </c>
     </row>
     <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B82">
-        <v>11.25072073258475</v>
+        <v>15.60889818841282</v>
       </c>
     </row>
     <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="B83">
-        <v>4.4596753101849131</v>
+        <v>11.25072073258475</v>
       </c>
     </row>
     <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="B84">
-        <v>3.0379217299305248</v>
+        <v>4.4596753101849131</v>
       </c>
     </row>
     <row r="85" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="B85">
-        <v>6.1651353618829177</v>
+        <v>3.0379217299305248</v>
       </c>
     </row>
     <row r="86" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B86">
-        <v>12.06557725833988</v>
+        <v>6.1651353618829177</v>
       </c>
     </row>
     <row r="87" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B87">
-        <v>6.1470308600513652</v>
+        <v>12.06557725833988</v>
       </c>
     </row>
     <row r="88" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="B88">
-        <v>68.761699641489798</v>
+        <v>6.1470308600513652</v>
       </c>
     </row>
     <row r="89" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B89">
-        <v>10.86218420870062</v>
+        <v>68.761699641489798</v>
       </c>
     </row>
     <row r="90" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B90">
-        <v>28.930923361529771</v>
+        <v>10.86218420870062</v>
       </c>
     </row>
     <row r="91" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="B91">
-        <v>11.40769894353671</v>
+        <v>28.930923361529771</v>
       </c>
     </row>
     <row r="92" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="B92">
-        <v>5.5735179627656608</v>
+        <v>11.40769894353671</v>
       </c>
     </row>
     <row r="93" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B93">
-        <v>15.346221468934351</v>
+        <v>5.5735179627656608</v>
       </c>
     </row>
     <row r="94" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B94">
-        <v>10.7722187048247</v>
+        <v>15.346221468934351</v>
       </c>
     </row>
     <row r="95" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B95">
-        <v>35.383594349907703</v>
+        <v>10.7722187048247</v>
       </c>
     </row>
     <row r="96" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="B96">
-        <v>98.981629368992984</v>
+        <v>35.383594349907703</v>
       </c>
     </row>
     <row r="97" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="B97">
-        <v>207.62726588094131</v>
+        <v>98.981629368992984</v>
       </c>
     </row>
     <row r="98" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="B98">
-        <v>515.60870539525365</v>
+        <v>207.62726588094131</v>
       </c>
     </row>
     <row r="99" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="B99">
-        <v>998.57619968483289</v>
+        <v>515.60870539525365</v>
       </c>
     </row>
     <row r="100" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="B100">
-        <v>637.58757138301951</v>
+        <v>998.57619968483289</v>
       </c>
     </row>
     <row r="101" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="B101">
-        <v>447.21001557633639</v>
+        <v>637.58757138301951</v>
       </c>
     </row>
     <row r="102" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B102">
-        <v>396.44541472195579</v>
+        <v>447.21001557633639</v>
       </c>
     </row>
     <row r="103" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="B103">
-        <v>262.92353876363097</v>
+        <v>396.44541472195579</v>
       </c>
     </row>
     <row r="104" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="B104">
-        <v>280.42919730997841</v>
+        <v>262.92353876363097</v>
       </c>
     </row>
     <row r="105" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B105">
-        <v>365.85184029458202</v>
+        <v>280.42919730997841</v>
       </c>
     </row>
     <row r="106" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B106">
-        <v>339.69247557783672</v>
+        <v>365.85184029458202</v>
       </c>
     </row>
     <row r="107" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B107">
-        <v>208.27067353409981</v>
+        <v>339.69247557783672</v>
       </c>
     </row>
     <row r="108" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B108">
-        <v>206.2121229753979</v>
+        <v>208.27067353409981</v>
       </c>
     </row>
     <row r="109" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B109">
-        <v>190.92635212919151</v>
+        <v>206.2121229753979</v>
       </c>
     </row>
     <row r="110" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B110">
-        <v>248.26047540758731</v>
+        <v>190.92635212919151</v>
       </c>
     </row>
     <row r="111" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B111">
-        <v>216.8596287526257</v>
+        <v>248.26047540758731</v>
       </c>
     </row>
     <row r="112" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="B112">
-        <v>177.2614251885368</v>
+        <v>216.8596287526257</v>
       </c>
     </row>
     <row r="113" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="B113">
-        <v>230.63397534202591</v>
+        <v>177.2614251885368</v>
       </c>
     </row>
     <row r="114" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B114">
-        <v>279.23959927560469</v>
+        <v>230.63397534202591</v>
       </c>
     </row>
     <row r="115" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B115">
-        <v>194.81405140056179</v>
+        <v>279.23959927560469</v>
       </c>
     </row>
     <row r="116" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B116">
-        <v>193.92640943688161</v>
+        <v>194.81405140056179</v>
       </c>
     </row>
     <row r="117" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B117">
-        <v>200.53043196805709</v>
+        <v>193.92640943688161</v>
       </c>
     </row>
     <row r="118" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B118">
-        <v>152.8915915821209</v>
+        <v>200.53043196805709</v>
       </c>
     </row>
     <row r="119" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="B119">
-        <v>127.3446016680591</v>
+        <v>152.8915915821209</v>
       </c>
     </row>
     <row r="120" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B120">
-        <v>126.09537667862421</v>
+        <v>127.3446016680591</v>
       </c>
     </row>
     <row r="121" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B121">
-        <v>166.118796181167</v>
+        <v>126.09537667862421</v>
       </c>
     </row>
     <row r="122" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B122">
-        <v>207.90359388553429</v>
+        <v>166.118796181167</v>
       </c>
     </row>
     <row r="123" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B123">
-        <v>192.7129842934261</v>
+        <v>207.90359388553429</v>
       </c>
     </row>
     <row r="124" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B124">
-        <v>177.8826002322543</v>
+        <v>192.7129842934261</v>
       </c>
     </row>
     <row r="125" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B125">
-        <v>117.49919407374431</v>
+        <v>177.8826002322543</v>
       </c>
     </row>
     <row r="126" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B126">
-        <v>157.33990078652349</v>
+        <v>117.49919407374431</v>
       </c>
     </row>
     <row r="127" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B127">
-        <v>132.4408146377269</v>
+        <v>157.33990078652349</v>
       </c>
     </row>
     <row r="128" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B128">
-        <v>283.70799201076687</v>
+        <v>132.4408146377269</v>
       </c>
     </row>
     <row r="129" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B129">
-        <v>165.6521507631409</v>
+        <v>283.70799201076687</v>
       </c>
     </row>
     <row r="130" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B130">
-        <v>142.3203134206955</v>
+        <v>165.6521507631409</v>
       </c>
     </row>
     <row r="131" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B131">
-        <v>245.92629323046251</v>
+        <v>142.3203134206955</v>
       </c>
     </row>
     <row r="132" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B132">
-        <v>177.88586048870559</v>
+        <v>245.92629323046251</v>
       </c>
     </row>
     <row r="133" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B133">
-        <v>124.2520385250878</v>
+        <v>177.88586048870559</v>
       </c>
     </row>
     <row r="134" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B134">
-        <v>234.95354837383019</v>
+        <v>124.2520385250878</v>
       </c>
     </row>
     <row r="135" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B135">
-        <v>302.51521742328782</v>
+        <v>234.95354837383019</v>
       </c>
     </row>
     <row r="136" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B136">
-        <v>195.38493790582879</v>
+        <v>302.51521742328782</v>
       </c>
     </row>
     <row r="137" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B137">
-        <v>151.84552114165379</v>
+        <v>195.38493790582879</v>
       </c>
     </row>
     <row r="138" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B138">
-        <v>192.51256628327761</v>
+        <v>151.84552114165379</v>
       </c>
     </row>
     <row r="139" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B139">
-        <v>175.601451385182</v>
+        <v>192.51256628327761</v>
       </c>
     </row>
     <row r="140" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B140">
-        <v>238.6573443674929</v>
+        <v>175.601451385182</v>
       </c>
     </row>
     <row r="141" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B141">
-        <v>209.94086513058051</v>
+        <v>238.6573443674929</v>
       </c>
     </row>
     <row r="142" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B142">
-        <v>170.8685225475007</v>
+        <v>209.94086513058051</v>
       </c>
     </row>
     <row r="143" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B143">
-        <v>181.52629061210459</v>
+        <v>170.8685225475007</v>
       </c>
     </row>
     <row r="144" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
+        <v>143</v>
+      </c>
+      <c r="B144">
+        <v>181.52629061210459</v>
+      </c>
+    </row>
+    <row r="145" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
         <v>144</v>
       </c>
-      <c r="B144">
+      <c r="B145">
         <v>192.50865767044689</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <phoneticPr fontId="2" type="noConversion"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>